--- a/sample/evidence/A-02-ghg-inventory-fy2025.xlsx
+++ b/sample/evidence/A-02-ghg-inventory-fy2025.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74 tCO2e/MWh (Peninsular, 2024)</t>
+          <t>0.74 tCO2e/MWh (Energy Commission provisional Peninsular 2024 GEF)</t>
         </is>
       </c>
       <c r="E5" t="n">
